--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-education-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-education-observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="510">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:28:06+00:00</t>
+    <t>2026-10-21T09:39:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1380,6 +1380,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -7270,7 +7274,7 @@
         <v>435</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>436</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
@@ -7279,10 +7283,10 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
@@ -7293,10 +7297,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7322,10 +7326,10 @@
         <v>432</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7376,7 +7380,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7388,7 +7392,7 @@
         <v>435</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>436</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
@@ -7397,10 +7401,10 @@
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
@@ -7411,10 +7415,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7440,16 +7444,16 @@
         <v>182</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7477,10 +7481,10 @@
         <v>117</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7498,7 +7502,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7516,10 +7520,10 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>369</v>
@@ -7533,10 +7537,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7562,16 +7566,16 @@
         <v>182</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7599,10 +7603,10 @@
         <v>270</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7620,7 +7624,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7638,10 +7642,10 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>369</v>
@@ -7655,10 +7659,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7681,17 +7685,17 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7740,7 +7744,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7764,7 +7768,7 @@
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
@@ -7775,10 +7779,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7804,10 +7808,10 @@
         <v>160</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7858,7 +7862,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7879,10 +7883,10 @@
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>21</v>
@@ -7893,10 +7897,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7919,16 +7923,16 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7978,7 +7982,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7999,10 +8003,10 @@
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>21</v>
@@ -8013,10 +8017,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8039,16 +8043,16 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8098,7 +8102,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8119,10 +8123,10 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
@@ -8133,10 +8137,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8162,16 +8166,16 @@
         <v>416</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8220,7 +8224,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8241,10 +8245,10 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>21</v>
@@ -8255,10 +8259,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8373,10 +8377,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8493,10 +8497,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8615,10 +8619,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8644,13 +8648,13 @@
         <v>182</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>268</v>
@@ -8702,7 +8706,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>93</v>
@@ -8720,7 +8724,7 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>275</v>
@@ -8737,10 +8741,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8763,16 +8767,16 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M57" t="s" s="2">
         <v>341</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>343</v>
@@ -8824,7 +8828,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8842,7 +8846,7 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>347</v>
@@ -8859,10 +8863,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8888,13 +8892,13 @@
         <v>182</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>354</v>
@@ -8946,7 +8950,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8981,10 +8985,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9068,7 +9072,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9103,10 +9107,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9132,10 +9136,10 @@
         <v>83</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>419</v>
@@ -9190,7 +9194,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
